--- a/data/2026_S_F_WG.xlsx
+++ b/data/2026_S_F_WG.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\word-tester\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{50F96465-786E-4F9B-8F60-C3E903D67B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29129FC9-F80A-4C67-8817-41C99A5E6BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{355F51DA-C17A-4A57-BF4D-C39486966AED}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="South Asia" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/data/2026_S_F_WG.xlsx
+++ b/data/2026_S_F_WG.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\word-tester\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29129FC9-F80A-4C67-8817-41C99A5E6BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80AB399D-8ADB-4E53-B26A-F0956028112C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{355F51DA-C17A-4A57-BF4D-C39486966AED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{355F51DA-C17A-4A57-BF4D-C39486966AED}"/>
   </bookViews>
   <sheets>
     <sheet name="South Asia" sheetId="1" r:id="rId1"/>
+    <sheet name="Australia and New Zealand" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="84">
   <si>
     <t>Word</t>
   </si>
@@ -156,6 +157,138 @@
   </si>
   <si>
     <t>the oppressed "untouchables" of Indian society (or: India’s “untouchables”; the lowest rung on the social ladder)</t>
+  </si>
+  <si>
+    <t>Outback</t>
+  </si>
+  <si>
+    <t>the most rural and isolated parts of Australia's Central Lowlands</t>
+  </si>
+  <si>
+    <t>monolith</t>
+  </si>
+  <si>
+    <t>a single standing stone (or: a single, massive, solid stone),</t>
+  </si>
+  <si>
+    <t>Aboriginal people</t>
+  </si>
+  <si>
+    <t>first humans to live in Australia</t>
+  </si>
+  <si>
+    <t>coral reef</t>
+  </si>
+  <si>
+    <t>a giant community of marine animals called corals (or: enormous underwater community of marine animals),</t>
+  </si>
+  <si>
+    <t>hot spring</t>
+  </si>
+  <si>
+    <t>pool of naturally occurring hot water</t>
+  </si>
+  <si>
+    <t>geyser</t>
+  </si>
+  <si>
+    <t>spouts of hot water that shoot from the ground</t>
+  </si>
+  <si>
+    <t>drought</t>
+  </si>
+  <si>
+    <t>long period of little or no rain</t>
+  </si>
+  <si>
+    <t>marsupial</t>
+  </si>
+  <si>
+    <t>mammal that raises its young in a pouch on the mother's body</t>
+  </si>
+  <si>
+    <t>eucalyptus</t>
+  </si>
+  <si>
+    <t>native Australian evergreen tree with stiff, pleasant-smelling leaves</t>
+  </si>
+  <si>
+    <t>boomerang</t>
+  </si>
+  <si>
+    <t>flat, bent, wooden weapon of the Australian Aborigines that is thrown to stun prey</t>
+  </si>
+  <si>
+    <t>dingo</t>
+  </si>
+  <si>
+    <t>species of domestic dog first brought to Australia from Asia (or: species of wild dog),</t>
+  </si>
+  <si>
+    <t>tikanga</t>
+  </si>
+  <si>
+    <t>traditional Maori customs and traditions passed down through generations</t>
+  </si>
+  <si>
+    <t>kapahaka</t>
+  </si>
+  <si>
+    <t>traditional art form of the Maori people that combines music, dance, singing, and facial expressions</t>
+  </si>
+  <si>
+    <t>station</t>
+  </si>
+  <si>
+    <t>cattle or sheep ranch in rural Australia (or: vast ranches that covered millions of acres in the Outback and other areas),</t>
+  </si>
+  <si>
+    <t>introduced species</t>
+  </si>
+  <si>
+    <t>non-native animals brought from other places</t>
+  </si>
+  <si>
+    <t>dominion</t>
+  </si>
+  <si>
+    <t>self-governing country within the British Empire</t>
+  </si>
+  <si>
+    <t>bush</t>
+  </si>
+  <si>
+    <t>large, undeveloped area where few people live</t>
+  </si>
+  <si>
+    <t>didgeridoo</t>
+  </si>
+  <si>
+    <t>Aboriginal musical instrument that is a long wood or bamboo tube</t>
+  </si>
+  <si>
+    <t>action song</t>
+  </si>
+  <si>
+    <t>performance combining body movement, music, and singing, often with lyrics celebrating Maori history and culture</t>
+  </si>
+  <si>
+    <t>geothermal energy</t>
+  </si>
+  <si>
+    <t>naturally occurring heat energy produced by hot liquid rock in Earth's upper mantle</t>
+  </si>
+  <si>
+    <t>kiwifruit</t>
+  </si>
+  <si>
+    <t>type of gooseberry fruit that is symbol of New Zealand</t>
+  </si>
+  <si>
+    <t>lawsuit</t>
+  </si>
+  <si>
+    <t>a legal case brought before a court of law</t>
   </si>
 </sst>
 </file>
@@ -741,4 +874,203 @@
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="95" orientation="landscape" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8E8EAE4-005E-4A1B-B0DE-ED9867E8166A}">
+  <dimension ref="A1:B23"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.5" customWidth="1"/>
+    <col min="2" max="2" width="107.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>